--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O781"/>
+  <dimension ref="A1:O799"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42331,7 +42331,7 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
@@ -42473,30 +42473,30 @@
         <v>3</v>
       </c>
       <c r="C765" t="n">
-        <v>20005</v>
+        <v>20007</v>
       </c>
       <c r="D765" t="n">
         <v>1</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="G765" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H765" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -42528,7 +42528,7 @@
         <v>4</v>
       </c>
       <c r="C766" t="n">
-        <v>20014</v>
+        <v>20385</v>
       </c>
       <c r="D766" t="n">
         <v>1</v>
@@ -42540,7 +42540,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G766" t="n">
@@ -42551,7 +42551,7 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
@@ -42583,7 +42583,7 @@
         <v>5</v>
       </c>
       <c r="C767" t="n">
-        <v>20385</v>
+        <v>20005</v>
       </c>
       <c r="D767" t="n">
         <v>1</v>
@@ -42595,7 +42595,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G767" t="n">
@@ -42606,7 +42606,7 @@
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -42638,19 +42638,19 @@
         <v>6</v>
       </c>
       <c r="C768" t="n">
-        <v>61377</v>
+        <v>20014</v>
       </c>
       <c r="D768" t="n">
         <v>1</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G768" t="n">
@@ -42661,7 +42661,7 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -42693,7 +42693,7 @@
         <v>7</v>
       </c>
       <c r="C769" t="n">
-        <v>20052</v>
+        <v>61377</v>
       </c>
       <c r="D769" t="n">
         <v>1</v>
@@ -42705,18 +42705,18 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G769" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H769" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
@@ -42748,7 +42748,7 @@
         <v>8</v>
       </c>
       <c r="C770" t="n">
-        <v>20007</v>
+        <v>20052</v>
       </c>
       <c r="D770" t="n">
         <v>1</v>
@@ -42760,7 +42760,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="G770" t="n">
@@ -42771,7 +42771,7 @@
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
@@ -42865,12 +42865,12 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G772" t="n">
@@ -42881,7 +42881,7 @@
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
@@ -42913,7 +42913,7 @@
         <v>11</v>
       </c>
       <c r="C773" t="n">
-        <v>60646</v>
+        <v>20013</v>
       </c>
       <c r="D773" t="n">
         <v>1</v>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G773" t="n">
@@ -42936,7 +42936,7 @@
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -42968,30 +42968,30 @@
         <v>12</v>
       </c>
       <c r="C774" t="n">
-        <v>20013</v>
+        <v>61590</v>
       </c>
       <c r="D774" t="n">
         <v>1</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba S.a.f.</t>
         </is>
       </c>
       <c r="G774" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H774" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -43023,19 +43023,19 @@
         <v>13</v>
       </c>
       <c r="C775" t="n">
-        <v>20001</v>
+        <v>60646</v>
       </c>
       <c r="D775" t="n">
         <v>1</v>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vasco da Gama Saf</t>
         </is>
       </c>
       <c r="G775" t="n">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -43188,7 +43188,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>61590</v>
+        <v>20001</v>
       </c>
       <c r="D778" t="n">
         <v>1</v>
@@ -43200,18 +43200,18 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G778" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H778" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -43365,7 +43365,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G781" t="n">
@@ -43397,6 +43397,996 @@
         <v>20</v>
       </c>
       <c r="O781" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="n">
+        <v>780</v>
+      </c>
+      <c r="B782" t="n">
+        <v>20</v>
+      </c>
+      <c r="C782" t="n">
+        <v>20007</v>
+      </c>
+      <c r="D782" t="n">
+        <v>2</v>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="G782" t="n">
+        <v>1</v>
+      </c>
+      <c r="H782" t="n">
+        <v>0</v>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K782" t="n">
+        <v>6</v>
+      </c>
+      <c r="L782" t="n">
+        <v>2</v>
+      </c>
+      <c r="M782" t="n">
+        <v>2</v>
+      </c>
+      <c r="N782" t="n">
+        <v>1</v>
+      </c>
+      <c r="O782" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="n">
+        <v>781</v>
+      </c>
+      <c r="B783" t="n">
+        <v>21</v>
+      </c>
+      <c r="C783" t="n">
+        <v>20002</v>
+      </c>
+      <c r="D783" t="n">
+        <v>2</v>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G783" t="n">
+        <v>5</v>
+      </c>
+      <c r="H783" t="n">
+        <v>1</v>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K783" t="n">
+        <v>4</v>
+      </c>
+      <c r="L783" t="n">
+        <v>1</v>
+      </c>
+      <c r="M783" t="n">
+        <v>4</v>
+      </c>
+      <c r="N783" t="n">
+        <v>2</v>
+      </c>
+      <c r="O783" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="n">
+        <v>782</v>
+      </c>
+      <c r="B784" t="n">
+        <v>22</v>
+      </c>
+      <c r="C784" t="n">
+        <v>20086</v>
+      </c>
+      <c r="D784" t="n">
+        <v>2</v>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G784" t="n">
+        <v>1</v>
+      </c>
+      <c r="H784" t="n">
+        <v>1</v>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K784" t="n">
+        <v>4</v>
+      </c>
+      <c r="L784" t="n">
+        <v>1</v>
+      </c>
+      <c r="M784" t="n">
+        <v>2</v>
+      </c>
+      <c r="N784" t="n">
+        <v>3</v>
+      </c>
+      <c r="O784" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="n">
+        <v>783</v>
+      </c>
+      <c r="B785" t="n">
+        <v>23</v>
+      </c>
+      <c r="C785" t="n">
+        <v>20385</v>
+      </c>
+      <c r="D785" t="n">
+        <v>2</v>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G785" t="n">
+        <v>2</v>
+      </c>
+      <c r="H785" t="n">
+        <v>2</v>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K785" t="n">
+        <v>4</v>
+      </c>
+      <c r="L785" t="n">
+        <v>1</v>
+      </c>
+      <c r="M785" t="n">
+        <v>1</v>
+      </c>
+      <c r="N785" t="n">
+        <v>4</v>
+      </c>
+      <c r="O785" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="n">
+        <v>784</v>
+      </c>
+      <c r="B786" t="n">
+        <v>24</v>
+      </c>
+      <c r="C786" t="n">
+        <v>20005</v>
+      </c>
+      <c r="D786" t="n">
+        <v>2</v>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G786" t="n">
+        <v>1</v>
+      </c>
+      <c r="H786" t="n">
+        <v>1</v>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K786" t="n">
+        <v>4</v>
+      </c>
+      <c r="L786" t="n">
+        <v>1</v>
+      </c>
+      <c r="M786" t="n">
+        <v>1</v>
+      </c>
+      <c r="N786" t="n">
+        <v>5</v>
+      </c>
+      <c r="O786" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="n">
+        <v>785</v>
+      </c>
+      <c r="B787" t="n">
+        <v>25</v>
+      </c>
+      <c r="C787" t="n">
+        <v>20014</v>
+      </c>
+      <c r="D787" t="n">
+        <v>2</v>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G787" t="n">
+        <v>1</v>
+      </c>
+      <c r="H787" t="n">
+        <v>1</v>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K787" t="n">
+        <v>4</v>
+      </c>
+      <c r="L787" t="n">
+        <v>1</v>
+      </c>
+      <c r="M787" t="n">
+        <v>1</v>
+      </c>
+      <c r="N787" t="n">
+        <v>6</v>
+      </c>
+      <c r="O787" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="n">
+        <v>786</v>
+      </c>
+      <c r="B788" t="n">
+        <v>26</v>
+      </c>
+      <c r="C788" t="n">
+        <v>61377</v>
+      </c>
+      <c r="D788" t="n">
+        <v>2</v>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G788" t="n">
+        <v>1</v>
+      </c>
+      <c r="H788" t="n">
+        <v>1</v>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K788" t="n">
+        <v>4</v>
+      </c>
+      <c r="L788" t="n">
+        <v>1</v>
+      </c>
+      <c r="M788" t="n">
+        <v>1</v>
+      </c>
+      <c r="N788" t="n">
+        <v>7</v>
+      </c>
+      <c r="O788" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="n">
+        <v>787</v>
+      </c>
+      <c r="B789" t="n">
+        <v>27</v>
+      </c>
+      <c r="C789" t="n">
+        <v>60175</v>
+      </c>
+      <c r="D789" t="n">
+        <v>2</v>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G789" t="n">
+        <v>3</v>
+      </c>
+      <c r="H789" t="n">
+        <v>5</v>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K789" t="n">
+        <v>3</v>
+      </c>
+      <c r="L789" t="n">
+        <v>1</v>
+      </c>
+      <c r="M789" t="n">
+        <v>2</v>
+      </c>
+      <c r="N789" t="n">
+        <v>8</v>
+      </c>
+      <c r="O789" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="n">
+        <v>788</v>
+      </c>
+      <c r="B790" t="n">
+        <v>28</v>
+      </c>
+      <c r="C790" t="n">
+        <v>20013</v>
+      </c>
+      <c r="D790" t="n">
+        <v>2</v>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G790" t="n">
+        <v>5</v>
+      </c>
+      <c r="H790" t="n">
+        <v>3</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K790" t="n">
+        <v>3</v>
+      </c>
+      <c r="L790" t="n">
+        <v>1</v>
+      </c>
+      <c r="M790" t="n">
+        <v>1</v>
+      </c>
+      <c r="N790" t="n">
+        <v>9</v>
+      </c>
+      <c r="O790" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="n">
+        <v>789</v>
+      </c>
+      <c r="B791" t="n">
+        <v>30</v>
+      </c>
+      <c r="C791" t="n">
+        <v>61590</v>
+      </c>
+      <c r="D791" t="n">
+        <v>2</v>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="G791" t="n">
+        <v>2</v>
+      </c>
+      <c r="H791" t="n">
+        <v>1</v>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K791" t="n">
+        <v>3</v>
+      </c>
+      <c r="L791" t="n">
+        <v>1</v>
+      </c>
+      <c r="M791" t="n">
+        <v>0</v>
+      </c>
+      <c r="N791" t="n">
+        <v>11</v>
+      </c>
+      <c r="O791" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="n">
+        <v>790</v>
+      </c>
+      <c r="B792" t="n">
+        <v>31</v>
+      </c>
+      <c r="C792" t="n">
+        <v>20018</v>
+      </c>
+      <c r="D792" t="n">
+        <v>2</v>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G792" t="n">
+        <v>1</v>
+      </c>
+      <c r="H792" t="n">
+        <v>5</v>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K792" t="n">
+        <v>3</v>
+      </c>
+      <c r="L792" t="n">
+        <v>1</v>
+      </c>
+      <c r="M792" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N792" t="n">
+        <v>12</v>
+      </c>
+      <c r="O792" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="n">
+        <v>791</v>
+      </c>
+      <c r="B793" t="n">
+        <v>32</v>
+      </c>
+      <c r="C793" t="n">
+        <v>59849</v>
+      </c>
+      <c r="D793" t="n">
+        <v>2</v>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Coritiba S.a.f.</t>
+        </is>
+      </c>
+      <c r="G793" t="n">
+        <v>2</v>
+      </c>
+      <c r="H793" t="n">
+        <v>1</v>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K793" t="n">
+        <v>3</v>
+      </c>
+      <c r="L793" t="n">
+        <v>1</v>
+      </c>
+      <c r="M793" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N793" t="n">
+        <v>13</v>
+      </c>
+      <c r="O793" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="n">
+        <v>792</v>
+      </c>
+      <c r="B794" t="n">
+        <v>33</v>
+      </c>
+      <c r="C794" t="n">
+        <v>60646</v>
+      </c>
+      <c r="D794" t="n">
+        <v>2</v>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Vasco da Gama Saf</t>
+        </is>
+      </c>
+      <c r="G794" t="n">
+        <v>1</v>
+      </c>
+      <c r="H794" t="n">
+        <v>1</v>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K794" t="n">
+        <v>1</v>
+      </c>
+      <c r="L794" t="n">
+        <v>0</v>
+      </c>
+      <c r="M794" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N794" t="n">
+        <v>14</v>
+      </c>
+      <c r="O794" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="n">
+        <v>793</v>
+      </c>
+      <c r="B795" t="n">
+        <v>34</v>
+      </c>
+      <c r="C795" t="n">
+        <v>20016</v>
+      </c>
+      <c r="D795" t="n">
+        <v>2</v>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G795" t="n">
+        <v>1</v>
+      </c>
+      <c r="H795" t="n">
+        <v>1</v>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K795" t="n">
+        <v>1</v>
+      </c>
+      <c r="L795" t="n">
+        <v>0</v>
+      </c>
+      <c r="M795" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N795" t="n">
+        <v>15</v>
+      </c>
+      <c r="O795" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="n">
+        <v>794</v>
+      </c>
+      <c r="B796" t="n">
+        <v>35</v>
+      </c>
+      <c r="C796" t="n">
+        <v>62194</v>
+      </c>
+      <c r="D796" t="n">
+        <v>2</v>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G796" t="n">
+        <v>0</v>
+      </c>
+      <c r="H796" t="n">
+        <v>1</v>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K796" t="n">
+        <v>1</v>
+      </c>
+      <c r="L796" t="n">
+        <v>0</v>
+      </c>
+      <c r="M796" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N796" t="n">
+        <v>16</v>
+      </c>
+      <c r="O796" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="n">
+        <v>795</v>
+      </c>
+      <c r="B797" t="n">
+        <v>36</v>
+      </c>
+      <c r="C797" t="n">
+        <v>20011</v>
+      </c>
+      <c r="D797" t="n">
+        <v>2</v>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G797" t="n">
+        <v>1</v>
+      </c>
+      <c r="H797" t="n">
+        <v>1</v>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K797" t="n">
+        <v>1</v>
+      </c>
+      <c r="L797" t="n">
+        <v>0</v>
+      </c>
+      <c r="M797" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N797" t="n">
+        <v>17</v>
+      </c>
+      <c r="O797" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="1" t="n">
+        <v>796</v>
+      </c>
+      <c r="B798" t="n">
+        <v>37</v>
+      </c>
+      <c r="C798" t="n">
+        <v>20008</v>
+      </c>
+      <c r="D798" t="n">
+        <v>2</v>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="G798" t="n">
+        <v>1</v>
+      </c>
+      <c r="H798" t="n">
+        <v>1</v>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K798" t="n">
+        <v>1</v>
+      </c>
+      <c r="L798" t="n">
+        <v>0</v>
+      </c>
+      <c r="M798" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N798" t="n">
+        <v>18</v>
+      </c>
+      <c r="O798" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="1" t="n">
+        <v>797</v>
+      </c>
+      <c r="B799" t="n">
+        <v>38</v>
+      </c>
+      <c r="C799" t="n">
+        <v>20022</v>
+      </c>
+      <c r="D799" t="n">
+        <v>2</v>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G799" t="n">
+        <v>2</v>
+      </c>
+      <c r="H799" t="n">
+        <v>2</v>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K799" t="n">
+        <v>1</v>
+      </c>
+      <c r="L799" t="n">
+        <v>0</v>
+      </c>
+      <c r="M799" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N799" t="n">
+        <v>19</v>
+      </c>
+      <c r="O799" t="n">
         <v>2026</v>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -16041,7 +16041,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -18230,7 +18230,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -19055,7 +19055,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -19605,7 +19605,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -21761,7 +21761,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G390" t="n">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G400" t="n">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G404" t="n">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -23015,7 +23015,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G411" t="n">
@@ -23136,7 +23136,7 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -23510,7 +23510,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G420" t="n">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G424" t="n">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G431" t="n">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -24390,7 +24390,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G440" t="n">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -24830,7 +24830,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G444" t="n">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G451" t="n">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G455" t="n">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -25611,7 +25611,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -25710,7 +25710,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G460" t="n">
@@ -25831,7 +25831,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G464" t="n">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -26271,7 +26271,7 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -26590,7 +26590,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -26810,7 +26810,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G484" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -27096,7 +27096,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -27415,7 +27415,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G494" t="n">
@@ -27591,7 +27591,7 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
@@ -27855,7 +27855,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G499" t="n">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -28031,7 +28031,7 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -28086,7 +28086,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -28130,7 +28130,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G504" t="n">
@@ -28416,7 +28416,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J509" t="inlineStr">
@@ -28515,7 +28515,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G511" t="n">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G515" t="n">
@@ -28966,7 +28966,7 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G520" t="n">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G524" t="n">
@@ -29461,7 +29461,7 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G532" t="n">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G535" t="n">
@@ -30000,7 +30000,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G538" t="n">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
@@ -30121,7 +30121,7 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -30176,7 +30176,7 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
@@ -30330,7 +30330,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G544" t="n">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
@@ -30660,7 +30660,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G550" t="n">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J550" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G555" t="n">
@@ -30946,7 +30946,7 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G559" t="n">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G564" t="n">
@@ -31441,7 +31441,7 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -31661,7 +31661,7 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
@@ -31705,7 +31705,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G569" t="n">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
@@ -32145,7 +32145,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G577" t="n">
@@ -32310,7 +32310,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G580" t="n">
@@ -32321,7 +32321,7 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
@@ -32486,7 +32486,7 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
@@ -32530,7 +32530,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G584" t="n">
@@ -32805,7 +32805,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G589" t="n">
@@ -33025,7 +33025,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -33091,7 +33091,7 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G604" t="n">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
@@ -33960,7 +33960,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -34180,7 +34180,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G614" t="n">
@@ -34301,7 +34301,7 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
@@ -34356,7 +34356,7 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G619" t="n">
@@ -34730,7 +34730,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -34851,7 +34851,7 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
@@ -34906,7 +34906,7 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G630" t="n">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G632" t="n">
@@ -35291,7 +35291,7 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
@@ -35555,7 +35555,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G639" t="n">
@@ -35830,7 +35830,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G644" t="n">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
@@ -36160,7 +36160,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G650" t="n">
@@ -36215,7 +36215,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G651" t="n">
@@ -36446,7 +36446,7 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
@@ -36666,7 +36666,7 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -36710,7 +36710,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G660" t="n">
@@ -36776,7 +36776,7 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
@@ -36831,7 +36831,7 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
@@ -36930,7 +36930,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G664" t="n">
@@ -37161,7 +37161,7 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -37370,7 +37370,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G672" t="n">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
@@ -37480,7 +37480,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G674" t="n">
@@ -37755,7 +37755,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G679" t="n">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
@@ -38030,7 +38030,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -38206,7 +38206,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -38426,7 +38426,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -38470,7 +38470,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G692" t="n">
@@ -38481,7 +38481,7 @@
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
@@ -38580,7 +38580,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -38855,7 +38855,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G699" t="n">
@@ -38866,7 +38866,7 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
@@ -39031,7 +39031,7 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
@@ -39130,7 +39130,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -39570,7 +39570,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G712" t="n">
@@ -39636,7 +39636,7 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
@@ -39680,7 +39680,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G714" t="n">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
@@ -39856,7 +39856,7 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G719" t="n">
@@ -40230,7 +40230,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G724" t="n">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
@@ -40461,7 +40461,7 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -40571,7 +40571,7 @@
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
@@ -40725,7 +40725,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G733" t="n">
@@ -40780,7 +40780,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G734" t="n">
@@ -40945,7 +40945,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -41330,7 +41330,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G744" t="n">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
@@ -41770,7 +41770,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G752" t="n">
@@ -41781,7 +41781,7 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -41836,7 +41836,7 @@
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>Cruzeiro Saf</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -41935,7 +41935,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>Vasco da Gama S.a.f.</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G755" t="n">
@@ -41946,7 +41946,7 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>Atlético Mineiro Saf</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Fortaleza Ec Saf</t>
+          <t>Fortaleza Ec</t>
         </is>
       </c>
       <c r="G759" t="n">
@@ -42496,7 +42496,7 @@
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -42551,7 +42551,7 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G774" t="n">
@@ -43035,7 +43035,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G775" t="n">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -43915,7 +43915,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G791" t="n">
@@ -44025,7 +44025,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>Coritiba S.a.f.</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G793" t="n">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Vasco da Gama Saf</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G794" t="n">

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O799"/>
+  <dimension ref="A1:O819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42473,30 +42473,30 @@
         <v>3</v>
       </c>
       <c r="C765" t="n">
-        <v>20007</v>
+        <v>20005</v>
       </c>
       <c r="D765" t="n">
         <v>1</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G765" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H765" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
@@ -42528,7 +42528,7 @@
         <v>4</v>
       </c>
       <c r="C766" t="n">
-        <v>20385</v>
+        <v>20014</v>
       </c>
       <c r="D766" t="n">
         <v>1</v>
@@ -42540,7 +42540,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G766" t="n">
@@ -42551,7 +42551,7 @@
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
@@ -42583,19 +42583,19 @@
         <v>5</v>
       </c>
       <c r="C767" t="n">
-        <v>20005</v>
+        <v>61377</v>
       </c>
       <c r="D767" t="n">
         <v>1</v>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G767" t="n">
@@ -42606,7 +42606,7 @@
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -42638,30 +42638,30 @@
         <v>6</v>
       </c>
       <c r="C768" t="n">
-        <v>20014</v>
+        <v>20052</v>
       </c>
       <c r="D768" t="n">
         <v>1</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="G768" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H768" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -42693,7 +42693,7 @@
         <v>7</v>
       </c>
       <c r="C769" t="n">
-        <v>61377</v>
+        <v>20007</v>
       </c>
       <c r="D769" t="n">
         <v>1</v>
@@ -42705,18 +42705,18 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="G769" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H769" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
@@ -42748,30 +42748,30 @@
         <v>8</v>
       </c>
       <c r="C770" t="n">
-        <v>20052</v>
+        <v>20385</v>
       </c>
       <c r="D770" t="n">
         <v>1</v>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G770" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H770" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
@@ -42865,23 +42865,23 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G772" t="n">
+        <v>2</v>
+      </c>
+      <c r="H772" t="n">
+        <v>2</v>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
           <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G772" t="n">
-        <v>2</v>
-      </c>
-      <c r="H772" t="n">
-        <v>2</v>
-      </c>
-      <c r="I772" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
@@ -42913,30 +42913,30 @@
         <v>11</v>
       </c>
       <c r="C773" t="n">
-        <v>20013</v>
+        <v>61590</v>
       </c>
       <c r="D773" t="n">
         <v>1</v>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G773" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H773" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
@@ -42968,30 +42968,30 @@
         <v>12</v>
       </c>
       <c r="C774" t="n">
-        <v>61590</v>
+        <v>20016</v>
       </c>
       <c r="D774" t="n">
         <v>1</v>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G774" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H774" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -43023,19 +43023,19 @@
         <v>13</v>
       </c>
       <c r="C775" t="n">
-        <v>60646</v>
+        <v>20001</v>
       </c>
       <c r="D775" t="n">
         <v>1</v>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G775" t="n">
@@ -43046,7 +43046,7 @@
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
@@ -43078,7 +43078,7 @@
         <v>14</v>
       </c>
       <c r="C776" t="n">
-        <v>20016</v>
+        <v>20013</v>
       </c>
       <c r="D776" t="n">
         <v>1</v>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G776" t="n">
@@ -43101,7 +43101,7 @@
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -43133,30 +43133,30 @@
         <v>15</v>
       </c>
       <c r="C777" t="n">
-        <v>20011</v>
+        <v>60646</v>
       </c>
       <c r="D777" t="n">
         <v>1</v>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G777" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>Athletico Paranaense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
@@ -43188,7 +43188,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="D778" t="n">
         <v>1</v>
@@ -43200,18 +43200,18 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G778" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H778" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
@@ -43243,7 +43243,7 @@
         <v>17</v>
       </c>
       <c r="C779" t="n">
-        <v>20008</v>
+        <v>20022</v>
       </c>
       <c r="D779" t="n">
         <v>1</v>
@@ -43255,18 +43255,18 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>Santos Fc</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G779" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H779" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
@@ -43298,7 +43298,7 @@
         <v>18</v>
       </c>
       <c r="C780" t="n">
-        <v>20022</v>
+        <v>20008</v>
       </c>
       <c r="D780" t="n">
         <v>1</v>
@@ -43310,18 +43310,18 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos Fc</t>
         </is>
       </c>
       <c r="G780" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H780" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
@@ -43408,7 +43408,7 @@
         <v>20</v>
       </c>
       <c r="C782" t="n">
-        <v>20007</v>
+        <v>20052</v>
       </c>
       <c r="D782" t="n">
         <v>2</v>
@@ -43420,18 +43420,18 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Athletico Paranaense</t>
         </is>
       </c>
       <c r="G782" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H782" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Santos Fc</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
@@ -43463,7 +43463,7 @@
         <v>21</v>
       </c>
       <c r="C783" t="n">
-        <v>20002</v>
+        <v>20007</v>
       </c>
       <c r="D783" t="n">
         <v>2</v>
@@ -43475,18 +43475,18 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="G783" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H783" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
@@ -43495,13 +43495,13 @@
         </is>
       </c>
       <c r="K783" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L783" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M783" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N783" t="n">
         <v>2</v>
@@ -43518,35 +43518,35 @@
         <v>22</v>
       </c>
       <c r="C784" t="n">
-        <v>20086</v>
+        <v>20002</v>
       </c>
       <c r="D784" t="n">
         <v>2</v>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G784" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H784" t="n">
         <v>1</v>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K784" t="n">
@@ -43556,7 +43556,7 @@
         <v>1</v>
       </c>
       <c r="M784" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N784" t="n">
         <v>3</v>
@@ -43573,7 +43573,7 @@
         <v>23</v>
       </c>
       <c r="C785" t="n">
-        <v>20385</v>
+        <v>20086</v>
       </c>
       <c r="D785" t="n">
         <v>2</v>
@@ -43585,18 +43585,18 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G785" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H785" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
@@ -43611,7 +43611,7 @@
         <v>1</v>
       </c>
       <c r="M785" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N785" t="n">
         <v>4</v>
@@ -43793,7 +43793,7 @@
         <v>27</v>
       </c>
       <c r="C789" t="n">
-        <v>60175</v>
+        <v>20385</v>
       </c>
       <c r="D789" t="n">
         <v>2</v>
@@ -43805,33 +43805,33 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G789" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H789" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="K789" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L789" t="n">
         <v>1</v>
       </c>
       <c r="M789" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N789" t="n">
         <v>8</v>
@@ -43848,35 +43848,35 @@
         <v>28</v>
       </c>
       <c r="C790" t="n">
-        <v>20013</v>
+        <v>60175</v>
       </c>
       <c r="D790" t="n">
         <v>2</v>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G790" t="n">
+        <v>3</v>
+      </c>
+      <c r="H790" t="n">
+        <v>5</v>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="G790" t="n">
-        <v>5</v>
-      </c>
-      <c r="H790" t="n">
-        <v>3</v>
-      </c>
-      <c r="I790" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K790" t="n">
@@ -43886,7 +43886,7 @@
         <v>1</v>
       </c>
       <c r="M790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N790" t="n">
         <v>9</v>
@@ -43900,33 +43900,33 @@
         <v>789</v>
       </c>
       <c r="B791" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C791" t="n">
-        <v>61590</v>
+        <v>20001</v>
       </c>
       <c r="D791" t="n">
         <v>2</v>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G791" t="n">
         <v>2</v>
       </c>
       <c r="H791" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
@@ -43941,10 +43941,10 @@
         <v>1</v>
       </c>
       <c r="M791" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N791" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O791" t="n">
         <v>2026</v>
@@ -43955,38 +43955,38 @@
         <v>790</v>
       </c>
       <c r="B792" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C792" t="n">
-        <v>20018</v>
+        <v>20013</v>
       </c>
       <c r="D792" t="n">
         <v>2</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G792" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H792" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>V</t>
         </is>
       </c>
       <c r="K792" t="n">
@@ -43996,10 +43996,10 @@
         <v>1</v>
       </c>
       <c r="M792" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="N792" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O792" t="n">
         <v>2026</v>
@@ -44010,10 +44010,10 @@
         <v>791</v>
       </c>
       <c r="B793" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C793" t="n">
-        <v>59849</v>
+        <v>61590</v>
       </c>
       <c r="D793" t="n">
         <v>2</v>
@@ -44051,10 +44051,10 @@
         <v>1</v>
       </c>
       <c r="M793" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="N793" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O793" t="n">
         <v>2026</v>
@@ -44065,51 +44065,51 @@
         <v>792</v>
       </c>
       <c r="B794" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C794" t="n">
-        <v>60646</v>
+        <v>20018</v>
       </c>
       <c r="D794" t="n">
         <v>2</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G794" t="n">
         <v>1</v>
       </c>
       <c r="H794" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K794" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L794" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M794" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N794" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O794" t="n">
         <v>2026</v>
@@ -44120,7 +44120,7 @@
         <v>793</v>
       </c>
       <c r="B795" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C795" t="n">
         <v>20016</v>
@@ -44164,7 +44164,7 @@
         <v>-1</v>
       </c>
       <c r="N795" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O795" t="n">
         <v>2026</v>
@@ -44175,7 +44175,7 @@
         <v>794</v>
       </c>
       <c r="B796" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C796" t="n">
         <v>62194</v>
@@ -44219,7 +44219,7 @@
         <v>-1</v>
       </c>
       <c r="N796" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O796" t="n">
         <v>2026</v>
@@ -44230,22 +44230,22 @@
         <v>795</v>
       </c>
       <c r="B797" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C797" t="n">
-        <v>20011</v>
+        <v>60646</v>
       </c>
       <c r="D797" t="n">
         <v>2</v>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G797" t="n">
@@ -44256,7 +44256,7 @@
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
@@ -44274,7 +44274,7 @@
         <v>-1</v>
       </c>
       <c r="N797" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O797" t="n">
         <v>2026</v>
@@ -44285,22 +44285,22 @@
         <v>796</v>
       </c>
       <c r="B798" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C798" t="n">
-        <v>20008</v>
+        <v>20011</v>
       </c>
       <c r="D798" t="n">
         <v>2</v>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>Santos Fc</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -44311,7 +44311,7 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
@@ -44326,10 +44326,10 @@
         <v>0</v>
       </c>
       <c r="M798" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N798" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O798" t="n">
         <v>2026</v>
@@ -44340,7 +44340,7 @@
         <v>797</v>
       </c>
       <c r="B799" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C799" t="n">
         <v>20022</v>
@@ -44384,9 +44384,1109 @@
         <v>-2</v>
       </c>
       <c r="N799" t="n">
+        <v>18</v>
+      </c>
+      <c r="O799" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="1" t="n">
+        <v>798</v>
+      </c>
+      <c r="B800" t="n">
+        <v>38</v>
+      </c>
+      <c r="C800" t="n">
+        <v>20008</v>
+      </c>
+      <c r="D800" t="n">
+        <v>2</v>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="G800" t="n">
+        <v>1</v>
+      </c>
+      <c r="H800" t="n">
+        <v>1</v>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K800" t="n">
+        <v>1</v>
+      </c>
+      <c r="L800" t="n">
+        <v>0</v>
+      </c>
+      <c r="M800" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N800" t="n">
         <v>19</v>
       </c>
-      <c r="O799" t="n">
+      <c r="O800" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="1" t="n">
+        <v>799</v>
+      </c>
+      <c r="B801" t="n">
+        <v>39</v>
+      </c>
+      <c r="C801" t="n">
+        <v>59849</v>
+      </c>
+      <c r="D801" t="n">
+        <v>2</v>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G801" t="n">
+        <v>1</v>
+      </c>
+      <c r="H801" t="n">
+        <v>2</v>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K801" t="n">
+        <v>0</v>
+      </c>
+      <c r="L801" t="n">
+        <v>0</v>
+      </c>
+      <c r="M801" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N801" t="n">
+        <v>20</v>
+      </c>
+      <c r="O801" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="B802" t="n">
+        <v>40</v>
+      </c>
+      <c r="C802" t="n">
+        <v>20002</v>
+      </c>
+      <c r="D802" t="n">
+        <v>3</v>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>3</v>
+      </c>
+      <c r="H802" t="n">
+        <v>1</v>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K802" t="n">
+        <v>7</v>
+      </c>
+      <c r="L802" t="n">
+        <v>2</v>
+      </c>
+      <c r="M802" t="n">
+        <v>6</v>
+      </c>
+      <c r="N802" t="n">
+        <v>1</v>
+      </c>
+      <c r="O802" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="1" t="n">
+        <v>801</v>
+      </c>
+      <c r="B803" t="n">
+        <v>41</v>
+      </c>
+      <c r="C803" t="n">
+        <v>20005</v>
+      </c>
+      <c r="D803" t="n">
+        <v>3</v>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>2</v>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K803" t="n">
+        <v>7</v>
+      </c>
+      <c r="L803" t="n">
+        <v>2</v>
+      </c>
+      <c r="M803" t="n">
+        <v>3</v>
+      </c>
+      <c r="N803" t="n">
+        <v>2</v>
+      </c>
+      <c r="O803" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="1" t="n">
+        <v>802</v>
+      </c>
+      <c r="B804" t="n">
+        <v>42</v>
+      </c>
+      <c r="C804" t="n">
+        <v>20014</v>
+      </c>
+      <c r="D804" t="n">
+        <v>3</v>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G804" t="n">
+        <v>1</v>
+      </c>
+      <c r="H804" t="n">
+        <v>0</v>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K804" t="n">
+        <v>7</v>
+      </c>
+      <c r="L804" t="n">
+        <v>2</v>
+      </c>
+      <c r="M804" t="n">
+        <v>2</v>
+      </c>
+      <c r="N804" t="n">
+        <v>3</v>
+      </c>
+      <c r="O804" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>803</v>
+      </c>
+      <c r="B805" t="n">
+        <v>43</v>
+      </c>
+      <c r="C805" t="n">
+        <v>61377</v>
+      </c>
+      <c r="D805" t="n">
+        <v>3</v>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G805" t="n">
+        <v>1</v>
+      </c>
+      <c r="H805" t="n">
+        <v>0</v>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K805" t="n">
+        <v>7</v>
+      </c>
+      <c r="L805" t="n">
+        <v>2</v>
+      </c>
+      <c r="M805" t="n">
+        <v>2</v>
+      </c>
+      <c r="N805" t="n">
+        <v>4</v>
+      </c>
+      <c r="O805" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>804</v>
+      </c>
+      <c r="B806" t="n">
+        <v>45</v>
+      </c>
+      <c r="C806" t="n">
+        <v>20007</v>
+      </c>
+      <c r="D806" t="n">
+        <v>3</v>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="G806" t="n">
+        <v>0</v>
+      </c>
+      <c r="H806" t="n">
+        <v>2</v>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K806" t="n">
+        <v>6</v>
+      </c>
+      <c r="L806" t="n">
+        <v>2</v>
+      </c>
+      <c r="M806" t="n">
+        <v>0</v>
+      </c>
+      <c r="N806" t="n">
+        <v>6</v>
+      </c>
+      <c r="O806" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>805</v>
+      </c>
+      <c r="B807" t="n">
+        <v>46</v>
+      </c>
+      <c r="C807" t="n">
+        <v>20086</v>
+      </c>
+      <c r="D807" t="n">
+        <v>3</v>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G807" t="n">
+        <v>3</v>
+      </c>
+      <c r="H807" t="n">
+        <v>3</v>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K807" t="n">
+        <v>5</v>
+      </c>
+      <c r="L807" t="n">
+        <v>1</v>
+      </c>
+      <c r="M807" t="n">
+        <v>2</v>
+      </c>
+      <c r="N807" t="n">
+        <v>7</v>
+      </c>
+      <c r="O807" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>806</v>
+      </c>
+      <c r="B808" t="n">
+        <v>47</v>
+      </c>
+      <c r="C808" t="n">
+        <v>20385</v>
+      </c>
+      <c r="D808" t="n">
+        <v>3</v>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G808" t="n">
+        <v>2</v>
+      </c>
+      <c r="H808" t="n">
+        <v>2</v>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K808" t="n">
+        <v>5</v>
+      </c>
+      <c r="L808" t="n">
+        <v>1</v>
+      </c>
+      <c r="M808" t="n">
+        <v>1</v>
+      </c>
+      <c r="N808" t="n">
+        <v>8</v>
+      </c>
+      <c r="O808" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>807</v>
+      </c>
+      <c r="B809" t="n">
+        <v>48</v>
+      </c>
+      <c r="C809" t="n">
+        <v>61590</v>
+      </c>
+      <c r="D809" t="n">
+        <v>3</v>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G809" t="n">
+        <v>3</v>
+      </c>
+      <c r="H809" t="n">
+        <v>3</v>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K809" t="n">
+        <v>4</v>
+      </c>
+      <c r="L809" t="n">
+        <v>1</v>
+      </c>
+      <c r="M809" t="n">
+        <v>0</v>
+      </c>
+      <c r="N809" t="n">
+        <v>9</v>
+      </c>
+      <c r="O809" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>808</v>
+      </c>
+      <c r="B810" t="n">
+        <v>49</v>
+      </c>
+      <c r="C810" t="n">
+        <v>20016</v>
+      </c>
+      <c r="D810" t="n">
+        <v>3</v>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G810" t="n">
+        <v>2</v>
+      </c>
+      <c r="H810" t="n">
+        <v>1</v>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K810" t="n">
+        <v>4</v>
+      </c>
+      <c r="L810" t="n">
+        <v>1</v>
+      </c>
+      <c r="M810" t="n">
+        <v>0</v>
+      </c>
+      <c r="N810" t="n">
+        <v>10</v>
+      </c>
+      <c r="O810" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>809</v>
+      </c>
+      <c r="B811" t="n">
+        <v>50</v>
+      </c>
+      <c r="C811" t="n">
+        <v>60175</v>
+      </c>
+      <c r="D811" t="n">
+        <v>3</v>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G811" t="n">
+        <v>0</v>
+      </c>
+      <c r="H811" t="n">
+        <v>1</v>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K811" t="n">
+        <v>3</v>
+      </c>
+      <c r="L811" t="n">
+        <v>1</v>
+      </c>
+      <c r="M811" t="n">
+        <v>1</v>
+      </c>
+      <c r="N811" t="n">
+        <v>11</v>
+      </c>
+      <c r="O811" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>810</v>
+      </c>
+      <c r="B812" t="n">
+        <v>52</v>
+      </c>
+      <c r="C812" t="n">
+        <v>20013</v>
+      </c>
+      <c r="D812" t="n">
+        <v>3</v>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G812" t="n">
+        <v>0</v>
+      </c>
+      <c r="H812" t="n">
+        <v>2</v>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K812" t="n">
+        <v>3</v>
+      </c>
+      <c r="L812" t="n">
+        <v>1</v>
+      </c>
+      <c r="M812" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N812" t="n">
+        <v>13</v>
+      </c>
+      <c r="O812" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>811</v>
+      </c>
+      <c r="B813" t="n">
+        <v>53</v>
+      </c>
+      <c r="C813" t="n">
+        <v>20018</v>
+      </c>
+      <c r="D813" t="n">
+        <v>3</v>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G813" t="n">
+        <v>1</v>
+      </c>
+      <c r="H813" t="n">
+        <v>2</v>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K813" t="n">
+        <v>3</v>
+      </c>
+      <c r="L813" t="n">
+        <v>1</v>
+      </c>
+      <c r="M813" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N813" t="n">
+        <v>14</v>
+      </c>
+      <c r="O813" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>812</v>
+      </c>
+      <c r="B814" t="n">
+        <v>54</v>
+      </c>
+      <c r="C814" t="n">
+        <v>62194</v>
+      </c>
+      <c r="D814" t="n">
+        <v>3</v>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G814" t="n">
+        <v>3</v>
+      </c>
+      <c r="H814" t="n">
+        <v>3</v>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K814" t="n">
+        <v>2</v>
+      </c>
+      <c r="L814" t="n">
+        <v>0</v>
+      </c>
+      <c r="M814" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N814" t="n">
+        <v>15</v>
+      </c>
+      <c r="O814" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>813</v>
+      </c>
+      <c r="B815" t="n">
+        <v>55</v>
+      </c>
+      <c r="C815" t="n">
+        <v>20022</v>
+      </c>
+      <c r="D815" t="n">
+        <v>3</v>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G815" t="n">
+        <v>3</v>
+      </c>
+      <c r="H815" t="n">
+        <v>3</v>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K815" t="n">
+        <v>2</v>
+      </c>
+      <c r="L815" t="n">
+        <v>0</v>
+      </c>
+      <c r="M815" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N815" t="n">
+        <v>16</v>
+      </c>
+      <c r="O815" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>814</v>
+      </c>
+      <c r="B816" t="n">
+        <v>56</v>
+      </c>
+      <c r="C816" t="n">
+        <v>60646</v>
+      </c>
+      <c r="D816" t="n">
+        <v>3</v>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G816" t="n">
+        <v>0</v>
+      </c>
+      <c r="H816" t="n">
+        <v>1</v>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K816" t="n">
+        <v>1</v>
+      </c>
+      <c r="L816" t="n">
+        <v>0</v>
+      </c>
+      <c r="M816" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N816" t="n">
+        <v>17</v>
+      </c>
+      <c r="O816" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="n">
+        <v>815</v>
+      </c>
+      <c r="B817" t="n">
+        <v>57</v>
+      </c>
+      <c r="C817" t="n">
+        <v>20008</v>
+      </c>
+      <c r="D817" t="n">
+        <v>3</v>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Santos Fc</t>
+        </is>
+      </c>
+      <c r="G817" t="n">
+        <v>1</v>
+      </c>
+      <c r="H817" t="n">
+        <v>2</v>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Athletico Paranaense</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K817" t="n">
+        <v>1</v>
+      </c>
+      <c r="L817" t="n">
+        <v>0</v>
+      </c>
+      <c r="M817" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N817" t="n">
+        <v>18</v>
+      </c>
+      <c r="O817" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>816</v>
+      </c>
+      <c r="B818" t="n">
+        <v>58</v>
+      </c>
+      <c r="C818" t="n">
+        <v>20011</v>
+      </c>
+      <c r="D818" t="n">
+        <v>3</v>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="G818" t="n">
+        <v>1</v>
+      </c>
+      <c r="H818" t="n">
+        <v>3</v>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K818" t="n">
+        <v>1</v>
+      </c>
+      <c r="L818" t="n">
+        <v>0</v>
+      </c>
+      <c r="M818" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N818" t="n">
+        <v>19</v>
+      </c>
+      <c r="O818" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="n">
+        <v>817</v>
+      </c>
+      <c r="B819" t="n">
+        <v>59</v>
+      </c>
+      <c r="C819" t="n">
+        <v>59849</v>
+      </c>
+      <c r="D819" t="n">
+        <v>3</v>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G819" t="n">
+        <v>2</v>
+      </c>
+      <c r="H819" t="n">
+        <v>2</v>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K819" t="n">
+        <v>1</v>
+      </c>
+      <c r="L819" t="n">
+        <v>0</v>
+      </c>
+      <c r="M819" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N819" t="n">
+        <v>20</v>
+      </c>
+      <c r="O819" t="n">
         <v>2026</v>
       </c>
     </row>
